--- a/Kachi_Gun/Table/Skin.xlsx
+++ b/Kachi_Gun/Table/Skin.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skin_Table_30" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skin_Table_17" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V32"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2024,1024 +2024,23 @@
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>기획서 25종 확장</t>
+          <t>구현 완료 (10-20 Skin_17 그림)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>사막 방랑자</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>1900</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>17250</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>320</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>184</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="M20" s="8" t="n">
-        <v>2784</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>1716</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>870</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>28.84</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_18</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_18</t>
-        </is>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_18</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>기획서 25종 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>설원 탐험가</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>2050</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>19300</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>352</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="M21" s="8" t="n">
-        <v>3136</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>1912</v>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>980</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>32.36</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_19</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_19</t>
-        </is>
-      </c>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_19</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>기획서 25종 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>네온 사이버</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="D22" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>21500</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>384</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>208</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>3520</v>
-      </c>
-      <c r="N22" s="8" t="n">
-        <v>2120</v>
-      </c>
-      <c r="O22" s="8" t="n">
-        <v>1100</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_20</t>
-        </is>
-      </c>
-      <c r="T22" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_20</t>
-        </is>
-      </c>
-      <c r="U22" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_20</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>기획서 25종 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>황금 갑옷</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>2350</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>23850</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>416</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="M23" s="8" t="n">
-        <v>3936</v>
-      </c>
-      <c r="N23" s="8" t="n">
-        <v>2340</v>
-      </c>
-      <c r="O23" s="8" t="n">
-        <v>1230</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>40.36</v>
-      </c>
-      <c r="Q23" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_21</t>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_21</t>
-        </is>
-      </c>
-      <c r="U23" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_21</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>기획서 25종 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>연금술사</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>26350</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>448</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="M24" s="8" t="n">
-        <v>4384</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>2572</v>
-      </c>
-      <c r="O24" s="8" t="n">
-        <v>1370</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>44.84</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>26.72</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_22</t>
-        </is>
-      </c>
-      <c r="T24" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_22</t>
-        </is>
-      </c>
-      <c r="U24" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_22</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>기획서 25종 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>우주 비행사</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>2650</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>29000</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>480</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>4864</v>
-      </c>
-      <c r="N25" s="8" t="n">
-        <v>2816</v>
-      </c>
-      <c r="O25" s="8" t="n">
-        <v>1520</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>49.64</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>29.16</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_23</t>
-        </is>
-      </c>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_23</t>
-        </is>
-      </c>
-      <c r="U25" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_23</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>기획서 25종 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>드래곤 나이트</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>2800</v>
-      </c>
-      <c r="F26" s="8" t="n">
-        <v>31800</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>512</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>5376</v>
-      </c>
-      <c r="N26" s="8" t="n">
-        <v>3072</v>
-      </c>
-      <c r="O26" s="8" t="n">
-        <v>1680</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>54.76</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>31.72</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_24</t>
-        </is>
-      </c>
-      <c r="T26" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_24</t>
-        </is>
-      </c>
-      <c r="U26" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_24</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>기획서 25종 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>사신 로브</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>3100</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>34900</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>576</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>5952</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>3343</v>
-      </c>
-      <c r="O27" s="8" t="n">
-        <v>1860</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>60.52</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>34.43</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_25</t>
-        </is>
-      </c>
-      <c r="T27" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_25</t>
-        </is>
-      </c>
-      <c r="U27" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_25</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr">
-        <is>
-          <t>150챕터 후반 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>발키리</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>3400</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>38300</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>640</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>286</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>6592</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>3629</v>
-      </c>
-      <c r="O28" s="8" t="n">
-        <v>2060</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>66.92</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_26</t>
-        </is>
-      </c>
-      <c r="T28" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_26</t>
-        </is>
-      </c>
-      <c r="U28" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_26</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>150챕터 후반 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>메카 카피</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>3700</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>42000</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>704</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>301</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>220</v>
-      </c>
-      <c r="M29" s="8" t="n">
-        <v>7296</v>
-      </c>
-      <c r="N29" s="8" t="n">
-        <v>3930</v>
-      </c>
-      <c r="O29" s="8" t="n">
-        <v>2280</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>73.95999999999999</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="R29" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_27</t>
-        </is>
-      </c>
-      <c r="T29" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_27</t>
-        </is>
-      </c>
-      <c r="U29" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_27</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>150챕터 후반 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>성좌의 수호자</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>46000</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>768</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>8064</v>
-      </c>
-      <c r="N30" s="8" t="n">
-        <v>4246</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>2520</v>
-      </c>
-      <c r="P30" s="3" t="n">
-        <v>81.64</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>43.46</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_28</t>
-        </is>
-      </c>
-      <c r="T30" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_28</t>
-        </is>
-      </c>
-      <c r="U30" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_28</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>150챕터 후반 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>차원 지배자</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>4300</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>50300</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>832</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>331</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>8896</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>4577</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>2780</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>89.95999999999999</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>46.77</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_29</t>
-        </is>
-      </c>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_29</t>
-        </is>
-      </c>
-      <c r="U31" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_29</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="inlineStr">
-        <is>
-          <t>150챕터 후반 확장</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>태초의 카피</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>4600</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>54900</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>896</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>346</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>9792</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>4923</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>3060</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>98.92</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>50.23</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>Char/skin_30</t>
-        </is>
-      </c>
-      <c r="T32" s="7" t="inlineStr">
-        <is>
-          <t>Char/gun_30</t>
-        </is>
-      </c>
-      <c r="U32" s="7" t="inlineStr">
-        <is>
-          <t>Art/Rig/c_30</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>150챕터 후반 확장</t>
-        </is>
-      </c>
-    </row>
+    <row r="20" ht="19" customHeight="1"/>
+    <row r="21" ht="19" customHeight="1"/>
+    <row r="22" ht="19" customHeight="1"/>
+    <row r="23" ht="19" customHeight="1"/>
+    <row r="24" ht="19" customHeight="1"/>
+    <row r="25" ht="19" customHeight="1"/>
+    <row r="26" ht="19" customHeight="1"/>
+    <row r="27" ht="19" customHeight="1"/>
+    <row r="28" ht="19" customHeight="1"/>
+    <row r="29" ht="19" customHeight="1"/>
+    <row r="30" ht="19" customHeight="1"/>
+    <row r="31" ht="19" customHeight="1"/>
+    <row r="32" ht="19" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
